--- a/input/procurement_v2_metadata.xlsx
+++ b/input/procurement_v2_metadata.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R206"/>
+  <dimension ref="A1:R239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Created,Approved,Sent,PartiallyReceived,Closed,Cancelled</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Open,Scheduled,PartiallyShipped,PartiallyReceived,Closed</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -10816,15 +10816,15 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>InventoryTransactionID</t>
+          <t>InventoryReceiptDetailID</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10867,7 +10867,7 @@
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>InventoryTransactionID primary key</t>
+          <t>InventoryReceiptDetailID primary key</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -10880,15 +10880,15 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -10952,15 +10952,15 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -11024,15 +11024,15 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -11096,15 +11096,15 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SupplierID</t>
+          <t>PurchaseOrderID</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>SupplierMaster</t>
+          <t>PurchaseOrderHdr</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>SupplierID</t>
+          <t>PurchaseOrderID</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -11155,7 +11155,7 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>SupplierID foreign key</t>
+          <t>PurchaseOrderID foreign key</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -11168,15 +11168,15 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>ComponentID</t>
+          <t>SupplierID</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>ComponentMaster</t>
+          <t>SupplierMaster</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>ComponentID</t>
+          <t>SupplierID</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -11227,7 +11227,7 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>ComponentID foreign key</t>
+          <t>SupplierID foreign key</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -11240,15 +11240,15 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>PlantID</t>
+          <t>ComponentID</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Plant</t>
+          <t>ComponentMaster</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>PlantID</t>
+          <t>ComponentID</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -11299,7 +11299,7 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>PlantID foreign key</t>
+          <t>ComponentID foreign key</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -11312,15 +11312,15 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>WarehouseID</t>
+          <t>PlantID</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11353,12 +11353,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Plant</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>WarehouseID</t>
+          <t>PlantID</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -11371,7 +11371,7 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>WarehouseID foreign key</t>
+          <t>PlantID foreign key</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -11384,15 +11384,15 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -11410,41 +11410,45 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>TransactionDate</t>
+          <t>WarehouseID</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>WarehouseID</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>TransactionDate</t>
+          <t>WarehouseID foreign key</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>date_offset</t>
+          <t>foreign_key</t>
         </is>
       </c>
       <c r="R168" t="inlineStr"/>
@@ -11452,15 +11456,15 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -11470,7 +11474,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -11478,12 +11482,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>TransactionType</t>
+          <t>POOrderDate</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>varchar(40)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -11494,21 +11498,25 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>StockIn</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>TransactionType</t>
+          <t>POOrderDate</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>calculated</t>
         </is>
       </c>
       <c r="R169" t="inlineStr"/>
@@ -11516,15 +11524,15 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -11534,7 +11542,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -11542,12 +11550,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>TransactionQuantity</t>
+          <t>ExpectedDeliveryDate</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -11559,40 +11567,40 @@
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="n">
-        <v>0</v>
-      </c>
-      <c r="O170" t="n">
-        <v>1000000</v>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Accepted quantity posted to inventory; equals InspectionResult.AcceptedQuantity</t>
+          <t>ExpectedDeliveryDate</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>decimal_range</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>InspectionResult.AcceptedQuantity</t>
-        </is>
-      </c>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -11602,7 +11610,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -11610,12 +11618,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>UnitPrice</t>
+          <t>ActualDeliveryDate</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -11627,40 +11635,40 @@
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="n">
-        <v>0</v>
-      </c>
-      <c r="O171" t="n">
-        <v>6000</v>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Unit price from PurchaseOrderLine.UnitPrice</t>
+          <t>ActualDeliveryDate</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>decimal_range</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>PurchaseOrderLine.UnitPrice</t>
-        </is>
-      </c>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -11670,7 +11678,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -11678,12 +11686,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>InventoryValue</t>
+          <t>StockPostedDate</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -11695,40 +11703,40 @@
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="n">
-        <v>0</v>
-      </c>
-      <c r="O172" t="n">
-        <v>100000000</v>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>InventoryValue</t>
+          <t>StockPostedDate</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>TransactionQuantity * UnitPrice</t>
-        </is>
-      </c>
+          <t>date_offset</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -11738,7 +11746,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -11746,12 +11754,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>ReferenceDocument</t>
+          <t>OrderedQuantity</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>varchar(80)</t>
+          <t>decimal(18,2)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -11763,32 +11771,40 @@
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>1000000</v>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>ReferenceDocument</t>
+          <t>Ordered quantity from PurchaseOrderLine.OrderedQuantity</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>PurchaseOrderLine.OrderedQuantity</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>InventoryTransaction</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inventory Transaction</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11798,7 +11814,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>inventory_transaction</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -11806,12 +11822,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>InventoryStatus</t>
+          <t>ShippedQuantity</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>varchar(40)</t>
+          <t>decimal(18,2)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -11822,67 +11838,67 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>Posted,QualityAccepted,ReceivedToInventory</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>1000000</v>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>InventoryStatus</t>
+          <t>Shipped quantity from ShipmentLine.ShippedQuantity</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>ShipmentLine.ShippedQuantity</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>85</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B175" t="n">
-        <v>95</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>InventoryID</t>
+          <t>ReceivedQuantity</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
@@ -11891,266 +11907,262 @@
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>1000000</v>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>InventoryID primary key</t>
+          <t>Received quantity from GoodsReceiptLine.ReceivedQuantity</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>sequence_id</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>GoodsReceiptLine.ReceivedQuantity</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>85</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B176" t="n">
-        <v>95</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>ComponentID</t>
+          <t>InspectedQuantity</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>ComponentMaster</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>ComponentID</t>
-        </is>
-      </c>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>1000000</v>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>ComponentID foreign key</t>
+          <t>Inspected quantity from InspectionResult.InspectedQuantity</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>foreign_key</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>InspectionResult.InspectedQuantity</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>85</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B177" t="n">
-        <v>95</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>PlantID</t>
+          <t>AcceptedQuantity</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>PlantID</t>
-        </is>
-      </c>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>1000000</v>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>PlantID foreign key</t>
+          <t>Accepted quantity from InspectionResult.AcceptedQuantity</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>foreign_key</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>InspectionResult.AcceptedQuantity</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>85</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B178" t="n">
-        <v>95</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>WarehouseID</t>
+          <t>RejectedQuantity</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>WarehouseID</t>
-        </is>
-      </c>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>1000000</v>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>WarehouseID foreign key</t>
+          <t>Rejected quantity from InspectionResult.RejectedQuantity</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>foreign_key</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>InspectionResult.RejectedQuantity</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>85</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B179" t="n">
-        <v>95</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>OnHandQuantity</t>
+          <t>OrderedUnitPrice</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12171,11 +12183,11 @@
         <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>1000000</v>
+        <v>6000</v>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>OnHandQuantity</t>
+          <t>Ordered unit price from PurchaseOrderLine.UnitPrice</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -12185,40 +12197,40 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>SUM(InventoryTransaction.TransactionQuantity) GROUP BY ComponentID, PlantID, WarehouseID</t>
+          <t>PurchaseOrderLine.UnitPrice</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>85</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B180" t="n">
-        <v>95</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>ReservedQuantity</t>
+          <t>DeliveredUnitPrice</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12239,11 +12251,11 @@
         <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>100000</v>
+        <v>6000</v>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>ReservedQuantity</t>
+          <t>Delivered unit price at receipt/invoice time</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -12256,33 +12268,33 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>85</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B181" t="n">
-        <v>95</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>AvailableQuantity</t>
+          <t>PriceDifference</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12300,14 +12312,14 @@
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="O181" t="n">
-        <v>1000000</v>
+        <v>6000</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>AvailableQuantity</t>
+          <t>PriceDifference</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
@@ -12317,45 +12329,45 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>OnHandQuantity - ReservedQuantity</t>
+          <t>DeliveredUnitPrice - OrderedUnitPrice</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>85</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B182" t="n">
-        <v>95</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>OnHandValue</t>
+          <t>PriceDifferencePct</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>decimal(9,4)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -12368,14 +12380,14 @@
       </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O182" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>OnHandValue</t>
+          <t>Price variance percentage based on stored PriceDifference</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -12385,40 +12397,40 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>SUM(InventoryTransaction.InventoryValue) GROUP BY ComponentID, PlantID, WarehouseID</t>
+          <t>CASE WHEN OrderedUnitPrice = 0 THEN 0 ELSE ROUND((PriceDifference / OrderedUnitPrice) * 100, 2) END</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>85</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B183" t="n">
-        <v>95</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>AvailableValue</t>
+          <t>OrderedValue</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12443,7 +12455,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>AvailableValue</t>
+          <t>OrderedValue</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -12453,45 +12465,45 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>AvailableQuantity * (OnHandValue / OnHandQuantity)</t>
+          <t>OrderedQuantity * OrderedUnitPrice</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>85</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B184" t="n">
-        <v>95</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>LastTransactionDate</t>
+          <t>DeliveredValue</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>decimal(18,2)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -12503,19 +12515,15 @@
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>100000000</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Last inventory transaction date</t>
+          <t>DeliveredValue</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -12525,45 +12533,45 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>MAX(InventoryTransaction.TransactionDate) GROUP BY ComponentID, PlantID, WarehouseID</t>
+          <t>ReceivedQuantity * DeliveredUnitPrice</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>85</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B185" t="n">
-        <v>95</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>LastUpdatedDate</t>
+          <t>AcceptedStockValue</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>decimal(18,2)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -12575,63 +12583,63 @@
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>100000000</v>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>LastUpdatedDate</t>
+          <t>AcceptedStockValue</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>date_range</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>AcceptedQuantity * DeliveredUnitPrice</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>InventoryReceiptDetail</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>85</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Inventory Receipt Detail</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B186" t="n">
-        <v>95</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Inventory Balance</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>InventoryStatus</t>
+          <t>OrderYear</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>varchar(40)</t>
+          <t>int</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -12642,55 +12650,59 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>Available,LowStock,OutOfStock,Hold</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O186" t="n">
+        <v>2025</v>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>InventoryStatus</t>
+          <t>YEAR(POOrderDate)</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>YEAR(POOrderDate)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SupplierInvoiceID</t>
+          <t>DeliveryYear</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12698,11 +12710,7 @@
           <t>int</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
@@ -12711,88 +12719,92 @@
         </is>
       </c>
       <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
+      <c r="N187" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O187" t="n">
+        <v>2025</v>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>SupplierInvoiceID primary key</t>
+          <t>YEAR(ActualDeliveryDate)</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>sequence_id</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>YEAR(ActualDeliveryDate)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>PurchaseOrderID</t>
+          <t>CrossYearDeliveryFlag</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>PurchaseOrderHdr</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>PurchaseOrderID</t>
-        </is>
-      </c>
+          <t>bit</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>PurchaseOrderID foreign key</t>
+          <t>0 for current 2025-only scope</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>foreign_key</t>
+          <t>category</t>
         </is>
       </c>
       <c r="R188" t="inlineStr"/>
@@ -12800,33 +12812,33 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SupplierID</t>
+          <t>DeliveryDelayDays</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12834,109 +12846,97 @@
           <t>int</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>SupplierMaster</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>SupplierID</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
+      <c r="N189" t="n">
+        <v>-365</v>
+      </c>
+      <c r="O189" t="n">
+        <v>365</v>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>SupplierID foreign key</t>
+          <t>ActualDeliveryDate - ExpectedDeliveryDate</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>foreign_key</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>ActualDeliveryDate - ExpectedDeliveryDate</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>GoodsReceiptID</t>
+          <t>DeliveryStatus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>GoodsReceiptHeader</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>GoodsReceiptID</t>
-        </is>
-      </c>
+          <t>varchar(40)</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>OnTime,Delayed,Early</t>
+        </is>
+      </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>GoodsReceiptID foreign key</t>
+          <t>DeliveryStatus</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>foreign_key</t>
+          <t>status</t>
         </is>
       </c>
       <c r="R190" t="inlineStr"/>
@@ -12944,38 +12944,38 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>InvoiceDate</t>
+          <t>PriceVarianceStatus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>varchar(40)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -12986,17 +12986,21 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>NoChange,PriceIncrease,PriceDecrease</t>
+        </is>
+      </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>InvoiceDate</t>
+          <t>PriceVarianceStatus</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>date_offset</t>
+          <t>status</t>
         </is>
       </c>
       <c r="R191" t="inlineStr"/>
@@ -13004,38 +13008,38 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryReceiptDetail</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Receipt Detail</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_receipt_detail</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DueDate</t>
+          <t>InventoryReceiptStatus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>varchar(40)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -13046,17 +13050,21 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>DueDate</t>
+          <t>InventoryReceiptStatus</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>date_offset</t>
+          <t>status</t>
         </is>
       </c>
       <c r="R192" t="inlineStr"/>
@@ -13064,41 +13072,45 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>InvoiceStatus</t>
+          <t>InventoryTransactionID</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>varchar(40)</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
@@ -13106,21 +13118,17 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>Draft,Submitted,Approved,PartiallyPaid,Paid,Overdue</t>
-        </is>
-      </c>
+      <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>InvoiceStatus</t>
+          <t>InventoryTransactionID primary key</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>sequence_id</t>
         </is>
       </c>
       <c r="R193" t="inlineStr"/>
@@ -13128,43 +13136,55 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>InvoiceAmount</t>
+          <t>InspectionResultID</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>InspectionResult</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>InspectionResultID</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>No</t>
@@ -13175,80 +13195,84 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>InvoiceAmount</t>
+          <t>InspectionResultID foreign key</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr">
-        <is>
-          <t>SUM(received PO value)</t>
-        </is>
-      </c>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>TaxAmount</t>
+          <t>GoodsReceiptLineID</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>GoodsReceiptLine</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>GoodsReceiptLineID</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="n">
-        <v>0</v>
-      </c>
-      <c r="O195" t="n">
-        <v>5000</v>
-      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>TaxAmount</t>
+          <t>GoodsReceiptLineID foreign key</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>decimal_range</t>
+          <t>foreign_key</t>
         </is>
       </c>
       <c r="R195" t="inlineStr"/>
@@ -13256,63 +13280,71 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>FreightAmount</t>
+          <t>PurchaseOrderLineID</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>PurchaseOrderLine</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PurchaseOrderLineID</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="n">
-        <v>0</v>
-      </c>
-      <c r="O196" t="n">
-        <v>3000</v>
-      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>FreightAmount</t>
+          <t>PurchaseOrderLineID foreign key</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>decimal_range</t>
+          <t>foreign_key</t>
         </is>
       </c>
       <c r="R196" t="inlineStr"/>
@@ -13320,43 +13352,55 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>TotalInvoiceAmount</t>
+          <t>SupplierID</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>SupplierMaster</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>SupplierID</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>No</t>
@@ -13367,80 +13411,84 @@
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>TotalInvoiceAmount</t>
+          <t>SupplierID foreign key</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr">
-        <is>
-          <t>InvoiceAmount + TaxAmount + FreightAmount</t>
-        </is>
-      </c>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Supplier Invoice</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>supplier_invoice</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>CurrencyCode</t>
+          <t>ComponentID</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>varchar(10)</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>ComponentMaster</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>ComponentID</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Currency code</t>
+          <t>ComponentID foreign key</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>foreign_key</t>
         </is>
       </c>
       <c r="R198" t="inlineStr"/>
@@ -13448,33 +13496,33 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PaymentTransaction</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Payment Transaction</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>payment_transaction</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>PaymentTransactionID</t>
+          <t>PlantID</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13484,11 +13532,19 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PlantID</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>No</t>
@@ -13499,12 +13555,12 @@
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>PaymentTransactionID primary key</t>
+          <t>PlantID foreign key</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>sequence_id</t>
+          <t>foreign_key</t>
         </is>
       </c>
       <c r="R199" t="inlineStr"/>
@@ -13512,33 +13568,33 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PaymentTransaction</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Payment Transaction</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>payment_transaction</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SupplierInvoiceID</t>
+          <t>WarehouseID</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13553,12 +13609,12 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>SupplierInvoice</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>SupplierInvoiceID</t>
+          <t>WarehouseID</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13571,7 +13627,7 @@
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>SupplierInvoiceID foreign key</t>
+          <t>WarehouseID foreign key</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -13584,71 +13640,67 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PaymentTransaction</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Payment Transaction</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>payment_transaction</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SupplierID</t>
+          <t>TransactionDate</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>SupplierMaster</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>SupplierID</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>SupplierID foreign key</t>
+          <t>TransactionDate</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>foreign_key</t>
+          <t>date_offset</t>
         </is>
       </c>
       <c r="R201" t="inlineStr"/>
@@ -13656,38 +13708,38 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PaymentTransaction</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Payment Transaction</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>payment_transaction</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>PaymentDate</t>
+          <t>TransactionType</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>varchar(40)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -13698,17 +13750,21 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>StockIn</t>
+        </is>
+      </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>PaymentDate</t>
+          <t>TransactionType</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>date_offset</t>
+          <t>status</t>
         </is>
       </c>
       <c r="R202" t="inlineStr"/>
@@ -13716,33 +13772,33 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PaymentTransaction</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Payment Transaction</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>payment_transaction</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>PaymentAmount</t>
+          <t>TransactionQuantity</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13767,7 +13823,7 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>PaymentAmount</t>
+          <t>Accepted quantity posted to inventory; equals InspectionResult.AcceptedQuantity</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
@@ -13775,43 +13831,47 @@
           <t>decimal_range</t>
         </is>
       </c>
-      <c r="R203" t="inlineStr"/>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>InspectionResult.AcceptedQuantity</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PaymentTransaction</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Payment Transaction</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>payment_transaction</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>PaymentMethod</t>
+          <t>UnitPrice</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>varchar(80)</t>
+          <t>decimal(18,2)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -13822,60 +13882,64 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>ACH,Wire Transfer,Check,Credit Transfer</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>6000</v>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>PaymentMethod</t>
+          <t>Unit price from PurchaseOrderLine.UnitPrice</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr"/>
+          <t>decimal_range</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>PurchaseOrderLine.UnitPrice</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PaymentTransaction</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Payment Transaction</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>payment_transaction</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>PaymentStatus</t>
+          <t>InventoryValue</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>varchar(40)</t>
+          <t>decimal(18,2)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -13886,60 +13950,64 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>Pending,Paid,PartiallyPaid,Failed</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>100000000</v>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>PaymentStatus</t>
+          <t>InventoryValue</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr"/>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>TransactionQuantity * UnitPrice</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PaymentTransaction</t>
+          <t>InventoryTransaction</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Payment Transaction</t>
+          <t>Inventory Transaction</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>payment_transaction</t>
+          <t>inventory_transaction</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1700</v>
+        <v>5500</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>CurrencyCode</t>
+          <t>ReferenceDocument</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>varchar(10)</t>
+          <t>varchar(80)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -13950,24 +14018,2212 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+      <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
+          <t>ReferenceDocument</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>InventoryTransaction</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>90</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Inventory Transaction</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>inventory_transaction</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>InventoryStatus</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>varchar(40)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Posted,QualityAccepted,ReceivedToInventory</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>InventoryStatus</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>95</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>InventoryID</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>InventoryID primary key</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>sequence_id</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>95</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ComponentID</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>ComponentMaster</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>ComponentID</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>ComponentID foreign key</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>95</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>PlantID</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>PlantID</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>PlantID foreign key</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>95</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>WarehouseID</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>WarehouseID</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>WarehouseID foreign key</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>95</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>OnHandQuantity</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>OnHandQuantity</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>SUM(InventoryTransaction.TransactionQuantity) GROUP BY ComponentID, PlantID, WarehouseID</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>95</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ReservedQuantity</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>100000</v>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>ReservedQuantity</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>decimal_range</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>95</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>AvailableQuantity</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>AvailableQuantity</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>OnHandQuantity - ReservedQuantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>95</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>OnHandValue</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>OnHandValue</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>SUM(InventoryTransaction.InventoryValue) GROUP BY ComponentID, PlantID, WarehouseID</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>95</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>AvailableValue</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>AvailableValue</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>AvailableQuantity * (OnHandValue / OnHandQuantity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>95</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>LastTransactionDate</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Last inventory transaction date</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>MAX(InventoryTransaction.TransactionDate) GROUP BY ComponentID, PlantID, WarehouseID</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>95</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>date_range</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>95</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Inventory Balance</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>InventoryStatus</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>varchar(40)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Available,LowStock,OutOfStock,Hold</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>InventoryStatus</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>100</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>SupplierInvoiceID</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>SupplierInvoiceID primary key</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>sequence_id</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>100</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>PurchaseOrderID</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>PurchaseOrderHdr</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>PurchaseOrderID</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>PurchaseOrderID foreign key</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>100</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>SupplierID</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>SupplierMaster</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>SupplierID</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>SupplierID foreign key</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>100</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>GoodsReceiptID</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>GoodsReceiptHeader</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>GoodsReceiptID</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>GoodsReceiptID foreign key</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>100</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>InvoiceDate</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>InvoiceDate</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>date_offset</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>100</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>DueDate</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>DueDate</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>date_offset</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>100</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>InvoiceStatus</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>varchar(40)</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Draft,Submitted,Approved,PartiallyPaid,Paid,Overdue</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>InvoiceStatus</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>100</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>InvoiceAmount</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>InvoiceAmount</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>SUM(received PO value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>100</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>TaxAmount</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>TaxAmount</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>decimal_range</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>100</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>FreightAmount</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>FreightAmount</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>decimal_range</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>100</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>TotalInvoiceAmount</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>TotalInvoiceAmount</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>InvoiceAmount + TaxAmount + FreightAmount</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>100</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Supplier Invoice</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>supplier_invoice</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>CurrencyCode</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
           <t>Currency code</t>
         </is>
       </c>
-      <c r="Q206" t="inlineStr">
+      <c r="Q231" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="R206" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>PaymentTransaction</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>110</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Payment Transaction</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>payment_transaction</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>PaymentTransactionID</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>PaymentTransactionID primary key</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>sequence_id</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PaymentTransaction</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>110</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Payment Transaction</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>payment_transaction</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>SupplierInvoiceID</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>SupplierInvoice</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>SupplierInvoiceID</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>SupplierInvoiceID foreign key</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PaymentTransaction</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>110</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Payment Transaction</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>payment_transaction</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>SupplierID</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>SupplierMaster</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>SupplierID</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>SupplierID foreign key</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PaymentTransaction</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>110</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Payment Transaction</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>payment_transaction</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>date_offset</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PaymentTransaction</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>110</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Payment Transaction</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>payment_transaction</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>PaymentAmount</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>decimal(18,2)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>PaymentAmount</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>decimal_range</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PaymentTransaction</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>110</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Payment Transaction</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>payment_transaction</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>PaymentMethod</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>ACH,Wire Transfer,Check,Credit Transfer</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>PaymentMethod</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>PaymentTransaction</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>110</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Payment Transaction</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>payment_transaction</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>PaymentStatus</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>varchar(40)</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Pending,Paid,PartiallyPaid,Failed</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>PaymentStatus</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>PaymentTransaction</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>110</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Payment Transaction</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>payment_transaction</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>CurrencyCode</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Currency code</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14002,7 +16258,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -14012,7 +16268,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>205</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
@@ -14022,7 +16278,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84242</v>
+        <v>89732</v>
       </c>
     </row>
   </sheetData>
